--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -1,99 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sai\Downloads\HOD-Project\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF8D7870-D38C-4FE5-A077-78CA6DD1DBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{F3949924-4A75-412D-B0C0-0CA8DA327D3C}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="12576" windowWidth="23256" xWindow="-108" yWindow="-108"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">Name </t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Feedback</t>
-  </si>
-  <si>
-    <t>National Conference</t>
-  </si>
-  <si>
-    <t>International Conference</t>
-  </si>
-  <si>
-    <t>National Journal</t>
-  </si>
-  <si>
-    <t>International Journal</t>
-  </si>
-  <si>
-    <t>UG guidance</t>
-  </si>
-  <si>
-    <t>PG Guidance</t>
-  </si>
-  <si>
-    <t>PHd student</t>
-  </si>
-  <si>
-    <t>Industry Collaboraation</t>
-  </si>
-  <si>
-    <t>org events</t>
-  </si>
-  <si>
-    <t>Attended events</t>
-  </si>
-  <si>
-    <t>Adminstraive Duties</t>
-  </si>
-  <si>
-    <t>Abi</t>
-  </si>
-  <si>
-    <t>CSE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -109,24 +43,83 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -426,108 +419,146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9CA2F2-ADCD-40CC-883A-FDA3812C045D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="15" max="15" width="17.77734375" customWidth="1"/>
+    <col customWidth="1" max="15" min="15" width="17.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name </t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>National Conference</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>International Conference</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>National Journal</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>International Journal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>UG guidance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PG Guidance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PHd student</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Industry Collaboraation</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>org events</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Attended events</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Adminstraive Duties</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Abi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -425,7 +425,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="15" min="15" width="17.77734375"/>
   </cols>
@@ -518,11 +518,15 @@
           <t>CSE</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -555,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -520,22 +520,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -544,22 +544,22 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible" windowHeight="12576" windowWidth="23256" xWindow="-108" yWindow="-108"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -43,15 +43,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -427,7 +427,7 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" max="15" min="15" width="17.77734375"/>
+    <col width="17.77734375" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -563,6 +563,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -520,19 +520,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -547,19 +547,19 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -520,12 +520,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -535,31 +535,31 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/appraisal.xlsx
+++ b/appraisal.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -425,9 +425,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
   <cols>
-    <col width="17.77734375" customWidth="1" min="15" max="15"/>
+    <col width="17.7109375" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,46 +520,46 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
